--- a/Produkty/997-50048997.xlsx
+++ b/Produkty/997-50048997.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -522,50 +522,9 @@
         <v/>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v/>
-      </c>
-      <c r="B4" t="str">
-        <v>525x20x28</v>
-      </c>
-      <c r="C4" t="str">
-        <v>525</v>
-      </c>
-      <c r="D4" t="str">
-        <v>28</v>
-      </c>
-      <c r="E4" t="str">
-        <v>20</v>
-      </c>
-      <c r="F4" t="str">
-        <v>BUK</v>
-      </c>
-      <c r="G4" t="str">
-        <v>1</v>
-      </c>
-      <c r="H4" t="str">
-        <v>3 i 4</v>
-      </c>
-      <c r="I4" t="str">
-        <v>1</v>
-      </c>
-      <c r="J4" t="str">
-        <v>2</v>
-      </c>
-      <c r="K4" t="str">
-        <v>1</v>
-      </c>
-      <c r="L4" t="str">
-        <v/>
-      </c>
-      <c r="M4" t="str">
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M3"/>
   </ignoredErrors>
 </worksheet>
 </file>